--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08E9334-D472-4AFA-A6A3-429F203CA542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98D0DB6D465E93D43A672875E70D84919" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{108795B6-0D09-4936-9233-7E72C6F627C7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 09-09-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 14-09-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -748,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98D0DB6D465E93D43A672875E70D84919" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{108795B6-0D09-4936-9233-7E72C6F627C7}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98D0DB6D465E93DEEFE34B03C71D84919" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E83E10C-832D-4150-B8DB-CFD71F1323BA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98D0DB6D465E93DEEFE34B03C71D84919" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E83E10C-832D-4150-B8DB-CFD71F1323BA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0812B622-95CF-43A7-BB32-C830142E35C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -748,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0812B622-95CF-43A7-BB32-C830142E35C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B178C1-B363-44DC-889B-F39E76C7D4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 14-09-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 17-09-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -748,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B178C1-B363-44DC-889B-F39E76C7D4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC1A946-848A-4BFC-B33A-1332D97F2CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC1A946-848A-4BFC-B33A-1332D97F2CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98D0DB6D465E93DF6C6729C3C70D84919" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA76FAAF-4D51-4301-B805-DB8CA0B519AC}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 17-09-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 21-09-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -748,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98D0DB6D465E93DF6C6729C3C70D84919" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA76FAAF-4D51-4301-B805-DB8CA0B519AC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933023E6-9652-4AD4-9DE0-23C44CADDDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -748,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933023E6-9652-4AD4-9DE0-23C44CADDDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6ABC04-1F47-4FB6-B55A-20289E8668BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 21-09-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 22-09-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6ABC04-1F47-4FB6-B55A-20289E8668BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4172B1-DCDE-41E3-A504-50B67C384BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 22-09-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 23-09-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4172B1-DCDE-41E3-A504-50B67C384BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9791D72C195E93DA6C6B49F8071D84919" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F50B5EB-0987-4B23-8B94-6A506F054DED}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 23-09-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 24-09-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -76,7 +76,7 @@
     <t>APD-DK (2.0.1)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -748,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9791D72C195E93DA6C6B49F8071D84919" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F50B5EB-0987-4B23-8B94-6A506F054DED}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020B852A-C89F-45B8-9B43-7E893180AE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 24-09-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 28-09-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -748,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6ABC04-1F47-4FB6-B55A-20289E8668BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51AB559C-D7F1-4AC1-B448-54A063F82E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 22-09-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 07-10-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -76,7 +76,7 @@
     <t>APD-DK (2.0.1)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020B852A-C89F-45B8-9B43-7E893180AE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA31D3E-FDF5-4652-9DF8-25713148E5A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 28-09-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 07-10-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA31D3E-FDF5-4652-9DF8-25713148E5A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9791D72C195E93D7D0E76BC3E70D849E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CAAABF0-40CD-40E7-A3E0-DD85016C6E4B}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 07-10-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 08-10-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9791D72C195E93D7D0E76BC3E70D849E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CAAABF0-40CD-40E7-A3E0-DD85016C6E4B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E532A72-F54C-428D-BCA7-996FAA7A4BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 08-10-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 09-10-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99E4367-FBAC-4C93-B66B-D65DED08D155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DF0D3BDA25E8258BD6B29B8470D84953" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA460424-F10C-4A37-AF70-CF8492EE8795}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 09-10-2026'!$A$1:$K$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 23-10-2026'!$A$1:$K$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
